--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -590,6 +590,1293 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6196</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7028</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11498</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10178</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8262</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7662</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7104</v>
+      </c>
+      <c r="I3" t="n">
+        <v>9821</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6544</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6167</v>
+      </c>
+      <c r="C4" t="n">
+        <v>6989</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11471</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10117</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8273</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7605</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7096</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9763</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6547</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6102</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7022</v>
+      </c>
+      <c r="D5" t="n">
+        <v>11515</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10034</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8291</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7696</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7143</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9753</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6489</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6128</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11473</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10016</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8341</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7773</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7128</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9715</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6521</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6139</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7055</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11572</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10028</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8370</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7802</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7075</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9783</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6539</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6216</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7035</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11487</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10116</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8447</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7720</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6996</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9866</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6628</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6188</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7006</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11534</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10163</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8363</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7769</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7034</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9943</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6649</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6175</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7049</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11471</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10137</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8407</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7731</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7104</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9969</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6612</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>6219</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7021</v>
+      </c>
+      <c r="D11" t="n">
+        <v>11431</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10053</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8328</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7829</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7103</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9871</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6533</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>6259</v>
+      </c>
+      <c r="C12" t="n">
+        <v>6974</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11378</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9985</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8262</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7799</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7128</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9774</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6522</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>6182</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7044</v>
+      </c>
+      <c r="D13" t="n">
+        <v>11407</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9930</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8235</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7797</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7111</v>
+      </c>
+      <c r="I13" t="n">
+        <v>9718</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6485</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>6133</v>
+      </c>
+      <c r="C14" t="n">
+        <v>6968</v>
+      </c>
+      <c r="D14" t="n">
+        <v>11340</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9833</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8173</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7716</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7039</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9757</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6454</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6194</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6996</v>
+      </c>
+      <c r="D15" t="n">
+        <v>11339</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9786</v>
+      </c>
+      <c r="F15" t="n">
+        <v>8116</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7789</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7078</v>
+      </c>
+      <c r="I15" t="n">
+        <v>9664</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6452</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>6221</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6972</v>
+      </c>
+      <c r="D16" t="n">
+        <v>11297</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9706</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8097</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7847</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7109</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9725</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6549</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>6174</v>
+      </c>
+      <c r="C17" t="n">
+        <v>6922</v>
+      </c>
+      <c r="D17" t="n">
+        <v>11389</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9620</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8130</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7748</v>
+      </c>
+      <c r="H17" t="n">
+        <v>7159</v>
+      </c>
+      <c r="I17" t="n">
+        <v>9655</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6509</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6250</v>
+      </c>
+      <c r="C18" t="n">
+        <v>6834</v>
+      </c>
+      <c r="D18" t="n">
+        <v>11468</v>
+      </c>
+      <c r="E18" t="n">
+        <v>9521</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8211</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7705</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7142</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9607</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6437</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6202</v>
+      </c>
+      <c r="C19" t="n">
+        <v>6883</v>
+      </c>
+      <c r="D19" t="n">
+        <v>11392</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9578</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8234</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7732</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7174</v>
+      </c>
+      <c r="I19" t="n">
+        <v>9598</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6506</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>6290</v>
+      </c>
+      <c r="C20" t="n">
+        <v>6931</v>
+      </c>
+      <c r="D20" t="n">
+        <v>11408</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9626</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8172</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7706</v>
+      </c>
+      <c r="H20" t="n">
+        <v>7167</v>
+      </c>
+      <c r="I20" t="n">
+        <v>9596</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6603</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>6355</v>
+      </c>
+      <c r="C21" t="n">
+        <v>6896</v>
+      </c>
+      <c r="D21" t="n">
+        <v>11361</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9702</v>
+      </c>
+      <c r="F21" t="n">
+        <v>8221</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7793</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7180</v>
+      </c>
+      <c r="I21" t="n">
+        <v>9621</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6588</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>6428</v>
+      </c>
+      <c r="C22" t="n">
+        <v>6944</v>
+      </c>
+      <c r="D22" t="n">
+        <v>11336</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9697</v>
+      </c>
+      <c r="F22" t="n">
+        <v>8246</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7810</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7165</v>
+      </c>
+      <c r="I22" t="n">
+        <v>9681</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6525</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>6402</v>
+      </c>
+      <c r="C23" t="n">
+        <v>6862</v>
+      </c>
+      <c r="D23" t="n">
+        <v>11362</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9797</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8297</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7774</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7228</v>
+      </c>
+      <c r="I23" t="n">
+        <v>9608</v>
+      </c>
+      <c r="J23" t="n">
+        <v>6502</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>6446</v>
+      </c>
+      <c r="C24" t="n">
+        <v>6956</v>
+      </c>
+      <c r="D24" t="n">
+        <v>11328</v>
+      </c>
+      <c r="E24" t="n">
+        <v>9859</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8364</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7830</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7141</v>
+      </c>
+      <c r="I24" t="n">
+        <v>9642</v>
+      </c>
+      <c r="J24" t="n">
+        <v>6463</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>6452</v>
+      </c>
+      <c r="C25" t="n">
+        <v>6996</v>
+      </c>
+      <c r="D25" t="n">
+        <v>11280</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9855</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8290</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7832</v>
+      </c>
+      <c r="H25" t="n">
+        <v>7127</v>
+      </c>
+      <c r="I25" t="n">
+        <v>9732</v>
+      </c>
+      <c r="J25" t="n">
+        <v>6373</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>6426</v>
+      </c>
+      <c r="C26" t="n">
+        <v>6936</v>
+      </c>
+      <c r="D26" t="n">
+        <v>11238</v>
+      </c>
+      <c r="E26" t="n">
+        <v>9886</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8192</v>
+      </c>
+      <c r="G26" t="n">
+        <v>7841</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7132</v>
+      </c>
+      <c r="I26" t="n">
+        <v>9739</v>
+      </c>
+      <c r="J26" t="n">
+        <v>6326</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>6339</v>
+      </c>
+      <c r="C27" t="n">
+        <v>7005</v>
+      </c>
+      <c r="D27" t="n">
+        <v>11244</v>
+      </c>
+      <c r="E27" t="n">
+        <v>9980</v>
+      </c>
+      <c r="F27" t="n">
+        <v>8107</v>
+      </c>
+      <c r="G27" t="n">
+        <v>7938</v>
+      </c>
+      <c r="H27" t="n">
+        <v>7172</v>
+      </c>
+      <c r="I27" t="n">
+        <v>9700</v>
+      </c>
+      <c r="J27" t="n">
+        <v>6258</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>6307</v>
+      </c>
+      <c r="C28" t="n">
+        <v>7104</v>
+      </c>
+      <c r="D28" t="n">
+        <v>11326</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9994</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8085</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>7087</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9718</v>
+      </c>
+      <c r="J28" t="n">
+        <v>6268</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>6401</v>
+      </c>
+      <c r="C29" t="n">
+        <v>7076</v>
+      </c>
+      <c r="D29" t="n">
+        <v>11397</v>
+      </c>
+      <c r="E29" t="n">
+        <v>9998</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8184</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8018</v>
+      </c>
+      <c r="H29" t="n">
+        <v>7108</v>
+      </c>
+      <c r="I29" t="n">
+        <v>9808</v>
+      </c>
+      <c r="J29" t="n">
+        <v>6317</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>6440</v>
+      </c>
+      <c r="C30" t="n">
+        <v>7051</v>
+      </c>
+      <c r="D30" t="n">
+        <v>11485</v>
+      </c>
+      <c r="E30" t="n">
+        <v>10015</v>
+      </c>
+      <c r="F30" t="n">
+        <v>8247</v>
+      </c>
+      <c r="G30" t="n">
+        <v>8085</v>
+      </c>
+      <c r="H30" t="n">
+        <v>7115</v>
+      </c>
+      <c r="I30" t="n">
+        <v>9848</v>
+      </c>
+      <c r="J30" t="n">
+        <v>6398</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>6403</v>
+      </c>
+      <c r="C31" t="n">
+        <v>6958</v>
+      </c>
+      <c r="D31" t="n">
+        <v>11532</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9943</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8242</v>
+      </c>
+      <c r="G31" t="n">
+        <v>8044</v>
+      </c>
+      <c r="H31" t="n">
+        <v>7121</v>
+      </c>
+      <c r="I31" t="n">
+        <v>9757</v>
+      </c>
+      <c r="J31" t="n">
+        <v>6323</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>6385</v>
+      </c>
+      <c r="C32" t="n">
+        <v>6870</v>
+      </c>
+      <c r="D32" t="n">
+        <v>11622</v>
+      </c>
+      <c r="E32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8163</v>
+      </c>
+      <c r="G32" t="n">
+        <v>8029</v>
+      </c>
+      <c r="H32" t="n">
+        <v>7100</v>
+      </c>
+      <c r="I32" t="n">
+        <v>9819</v>
+      </c>
+      <c r="J32" t="n">
+        <v>6338</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>6415</v>
+      </c>
+      <c r="C33" t="n">
+        <v>6893</v>
+      </c>
+      <c r="D33" t="n">
+        <v>11645</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9913</v>
+      </c>
+      <c r="F33" t="n">
+        <v>8236</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8104</v>
+      </c>
+      <c r="H33" t="n">
+        <v>7030</v>
+      </c>
+      <c r="I33" t="n">
+        <v>9917</v>
+      </c>
+      <c r="J33" t="n">
+        <v>6330</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>6454</v>
+      </c>
+      <c r="C34" t="n">
+        <v>6880</v>
+      </c>
+      <c r="D34" t="n">
+        <v>11737</v>
+      </c>
+      <c r="E34" t="n">
+        <v>9926</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8261</v>
+      </c>
+      <c r="G34" t="n">
+        <v>8086</v>
+      </c>
+      <c r="H34" t="n">
+        <v>6981</v>
+      </c>
+      <c r="I34" t="n">
+        <v>9964</v>
+      </c>
+      <c r="J34" t="n">
+        <v>6314</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C35" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D35" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E35" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F35" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H35" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I35" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J35" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -552,39 +552,39 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" t="n">
         <v>6200</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" t="n">
         <v>7000</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" t="n">
         <v>11500</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" t="n">
         <v>10200</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" t="n">
         <v>8300</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="G2" t="n">
         <v>7700</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="H2" t="n">
         <v>7100</v>
       </c>
-      <c r="I2" s="6" t="n">
+      <c r="I2" t="n">
         <v>9800</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="J2" t="n">
         <v>6500</v>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>estimasi terakhir</t>
         </is>
@@ -1874,6 +1874,84 @@
       <c r="K35" t="inlineStr">
         <is>
           <t>estimasi terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C36" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D36" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E36" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F36" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I36" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J36" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
         </is>
       </c>
     </row>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1955,6 +1955,84 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2033,6 +2033,45 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2072,45 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harga Komoditas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga Komoditas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1916,201 +1916,6 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C37" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E37" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I37" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J37" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K37" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C38" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E38" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G38" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J38" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E39" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G39" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I39" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J39" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C40" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D40" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E40" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G40" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H40" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I40" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J40" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K40" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D41" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E41" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H41" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I41" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J41" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K41" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga Komoditas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harga Komoditas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1916,6 +1916,7338 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K56" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K60" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I61" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I62" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I64" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J64" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I65" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I66" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J66" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I67" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I68" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J68" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G69" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I69" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J69" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I70" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J70" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G71" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H71" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I71" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J71" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I72" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J72" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K72" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I73" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G74" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I74" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J74" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K74" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G75" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I75" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J75" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I76" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J76" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K76" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D77" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G77" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I77" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J77" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D78" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G78" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I78" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J78" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K78" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C79" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D79" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E79" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G79" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I79" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J79" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D80" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E80" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G80" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I80" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J80" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K80" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C81" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D81" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G81" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I81" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J81" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D82" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G82" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H82" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I82" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J82" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K82" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C83" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D83" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E83" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G83" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H83" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I83" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J83" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D84" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G84" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H84" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I84" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J84" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K84" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C85" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D85" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G85" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H85" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I85" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J85" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K85" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D86" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E86" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G86" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H86" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I86" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D87" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E87" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G87" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H87" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I87" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D88" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E88" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F88" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G88" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H88" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I88" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J88" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K88" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C89" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D89" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E89" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F89" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G89" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H89" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I89" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J89" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D90" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E90" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F90" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G90" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I90" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J90" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K90" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C91" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D91" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E91" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F91" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G91" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H91" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I91" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J91" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K91" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D92" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G92" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H92" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I92" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J92" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K92" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C93" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D93" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E93" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G93" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H93" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I93" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J93" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K93" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D94" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E94" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G94" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H94" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I94" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J94" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K94" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C95" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D95" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E95" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G95" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H95" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I95" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J95" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D96" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G96" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I96" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J96" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K96" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C97" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D97" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E97" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G97" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H97" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I97" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J97" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D98" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E98" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F98" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G98" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H98" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I98" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J98" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K98" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C99" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D99" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E99" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G99" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H99" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I99" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J99" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K99" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D100" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E100" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G100" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H100" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I100" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J100" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K100" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C101" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D101" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E101" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F101" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G101" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H101" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I101" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J101" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K101" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D102" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E102" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F102" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G102" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H102" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I102" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J102" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K102" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C103" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D103" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E103" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G103" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H103" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I103" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J103" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D104" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E104" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F104" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G104" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H104" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I104" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J104" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K104" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C105" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D105" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E105" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F105" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G105" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H105" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I105" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J105" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K105" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D106" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E106" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F106" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G106" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H106" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I106" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J106" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K106" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C107" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D107" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E107" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F107" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G107" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H107" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I107" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J107" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K107" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C108" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D108" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E108" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F108" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G108" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H108" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I108" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J108" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K108" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C109" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D109" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E109" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F109" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G109" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H109" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I109" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J109" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K109" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C110" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D110" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E110" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F110" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G110" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H110" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I110" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J110" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K110" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C111" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D111" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E111" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F111" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G111" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H111" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I111" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J111" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K111" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C112" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D112" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E112" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F112" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G112" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H112" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I112" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J112" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K112" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C113" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D113" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E113" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F113" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G113" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H113" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I113" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J113" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K113" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C114" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D114" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E114" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F114" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G114" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H114" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I114" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J114" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K114" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C115" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D115" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E115" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F115" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G115" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H115" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I115" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J115" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K115" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C116" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D116" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E116" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F116" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G116" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H116" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I116" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J116" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K116" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C117" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D117" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E117" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F117" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G117" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H117" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I117" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J117" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K117" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C118" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D118" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E118" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F118" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G118" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H118" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I118" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J118" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K118" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C119" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D119" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E119" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F119" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G119" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H119" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I119" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J119" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K119" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C120" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D120" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E120" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F120" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G120" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H120" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I120" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J120" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K120" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C121" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D121" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E121" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F121" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G121" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H121" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I121" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J121" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K121" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C122" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D122" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E122" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F122" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G122" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H122" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I122" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J122" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K122" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C123" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D123" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E123" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G123" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H123" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I123" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J123" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K123" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C124" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D124" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E124" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F124" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G124" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H124" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I124" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J124" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K124" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C125" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D125" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E125" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F125" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G125" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H125" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I125" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J125" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K125" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C126" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D126" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E126" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F126" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G126" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H126" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I126" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J126" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K126" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C127" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D127" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E127" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F127" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G127" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H127" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I127" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J127" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K127" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C128" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D128" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E128" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F128" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G128" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H128" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I128" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J128" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K128" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C129" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D129" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E129" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F129" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G129" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H129" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I129" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J129" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K129" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C130" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D130" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E130" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F130" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G130" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H130" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I130" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J130" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K130" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C131" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D131" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E131" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F131" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G131" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H131" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I131" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J131" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K131" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C132" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D132" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E132" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F132" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G132" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H132" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I132" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J132" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K132" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C133" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D133" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E133" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F133" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G133" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H133" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I133" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J133" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K133" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C134" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D134" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E134" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F134" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G134" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H134" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I134" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J134" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K134" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C135" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D135" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E135" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F135" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G135" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H135" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I135" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J135" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K135" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C136" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D136" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E136" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F136" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G136" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H136" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I136" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J136" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K136" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C137" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D137" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E137" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F137" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G137" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H137" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I137" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J137" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K137" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C138" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D138" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E138" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F138" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G138" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H138" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I138" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J138" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K138" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C139" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D139" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E139" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F139" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G139" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H139" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I139" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J139" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K139" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C140" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D140" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E140" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F140" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G140" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H140" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I140" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J140" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K140" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C141" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D141" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E141" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F141" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G141" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H141" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I141" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J141" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K141" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C142" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D142" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E142" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F142" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G142" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H142" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I142" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J142" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K142" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C143" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D143" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E143" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F143" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G143" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H143" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I143" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J143" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K143" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C144" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D144" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E144" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F144" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G144" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H144" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I144" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J144" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K144" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C145" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D145" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E145" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F145" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G145" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H145" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I145" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J145" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K145" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C146" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D146" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E146" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F146" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G146" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H146" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I146" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J146" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K146" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C147" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D147" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E147" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F147" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G147" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H147" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I147" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J147" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K147" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C148" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D148" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E148" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F148" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G148" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H148" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I148" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J148" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K148" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C149" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D149" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E149" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F149" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G149" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H149" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I149" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J149" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K149" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C150" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D150" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E150" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F150" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G150" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H150" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I150" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J150" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K150" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C151" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D151" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E151" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F151" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G151" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H151" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I151" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J151" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K151" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C152" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D152" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E152" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F152" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G152" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H152" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I152" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J152" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K152" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C153" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D153" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E153" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F153" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G153" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H153" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I153" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J153" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K153" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C154" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D154" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E154" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F154" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G154" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H154" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I154" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J154" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K154" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C155" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D155" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E155" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F155" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G155" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H155" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I155" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J155" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K155" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C156" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D156" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E156" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F156" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G156" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H156" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I156" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J156" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K156" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C157" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D157" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E157" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F157" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G157" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H157" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I157" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J157" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K157" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C158" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D158" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E158" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F158" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G158" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H158" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I158" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J158" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K158" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C159" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D159" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E159" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F159" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G159" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H159" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I159" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J159" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K159" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C160" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D160" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E160" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F160" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G160" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H160" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I160" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J160" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K160" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C161" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D161" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E161" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F161" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G161" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H161" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I161" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J161" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K161" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C162" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D162" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E162" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F162" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G162" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H162" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I162" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J162" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K162" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C163" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D163" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E163" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F163" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G163" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H163" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I163" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J163" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K163" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B164" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C164" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D164" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E164" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F164" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G164" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H164" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I164" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J164" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K164" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C165" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D165" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E165" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F165" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G165" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H165" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I165" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J165" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K165" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C166" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D166" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E166" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F166" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G166" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H166" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I166" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J166" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K166" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B167" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C167" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D167" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E167" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F167" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G167" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H167" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I167" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J167" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K167" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C168" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D168" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E168" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F168" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G168" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H168" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I168" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J168" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K168" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C169" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D169" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E169" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F169" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G169" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H169" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I169" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J169" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K169" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C170" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D170" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E170" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F170" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G170" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H170" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I170" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J170" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K170" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B171" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C171" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D171" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E171" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F171" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G171" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H171" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I171" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J171" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K171" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B172" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C172" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D172" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E172" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F172" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G172" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H172" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I172" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J172" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K172" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B173" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C173" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D173" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E173" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F173" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G173" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H173" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I173" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J173" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K173" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B174" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C174" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D174" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E174" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F174" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G174" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H174" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I174" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J174" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K174" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C175" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D175" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E175" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F175" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G175" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H175" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I175" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J175" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K175" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B176" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C176" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D176" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E176" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F176" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G176" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H176" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I176" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J176" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K176" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B177" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C177" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D177" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E177" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F177" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G177" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H177" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I177" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J177" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K177" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C178" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D178" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E178" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F178" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G178" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H178" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I178" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J178" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K178" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B179" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C179" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D179" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E179" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F179" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G179" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H179" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I179" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J179" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K179" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C180" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D180" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E180" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F180" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G180" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H180" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I180" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J180" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K180" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C181" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D181" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E181" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F181" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G181" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H181" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I181" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J181" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K181" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C182" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D182" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E182" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F182" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G182" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H182" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I182" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J182" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K182" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C183" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D183" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E183" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F183" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G183" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H183" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I183" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J183" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K183" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C184" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D184" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E184" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F184" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G184" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H184" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I184" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J184" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K184" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C185" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D185" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E185" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F185" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G185" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H185" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I185" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J185" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K185" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C186" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D186" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E186" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F186" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G186" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H186" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I186" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J186" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K186" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C187" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D187" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E187" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F187" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G187" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H187" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I187" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J187" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K187" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C188" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D188" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E188" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F188" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G188" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H188" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I188" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J188" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K188" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C189" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D189" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E189" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F189" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G189" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H189" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I189" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J189" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K189" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C190" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D190" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E190" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F190" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G190" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H190" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I190" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J190" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K190" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B191" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C191" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D191" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E191" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F191" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G191" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H191" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I191" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J191" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K191" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B192" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C192" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D192" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E192" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F192" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G192" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H192" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I192" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J192" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K192" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B193" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C193" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D193" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E193" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F193" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G193" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H193" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I193" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J193" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K193" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B194" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C194" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D194" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E194" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F194" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G194" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H194" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I194" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J194" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K194" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B195" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C195" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D195" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E195" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F195" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G195" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H195" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I195" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J195" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K195" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B196" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C196" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D196" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E196" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F196" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G196" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H196" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I196" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J196" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K196" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C197" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D197" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E197" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F197" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G197" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H197" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I197" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J197" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K197" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C198" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D198" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E198" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F198" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G198" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H198" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I198" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J198" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K198" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C199" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D199" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E199" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F199" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G199" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H199" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I199" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J199" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K199" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B200" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C200" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D200" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E200" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F200" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G200" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H200" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I200" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J200" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K200" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C201" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D201" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E201" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F201" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G201" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H201" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I201" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J201" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K201" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B202" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C202" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D202" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E202" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F202" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G202" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H202" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I202" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J202" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K202" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B203" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C203" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D203" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E203" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F203" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G203" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H203" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I203" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J203" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K203" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C204" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D204" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E204" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F204" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G204" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H204" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I204" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J204" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K204" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B205" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C205" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D205" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E205" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F205" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G205" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H205" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I205" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J205" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K205" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B206" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C206" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D206" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E206" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F206" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G206" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H206" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I206" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J206" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K206" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B207" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C207" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D207" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E207" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F207" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G207" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H207" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I207" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J207" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K207" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B208" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C208" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D208" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E208" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F208" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G208" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H208" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I208" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J208" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K208" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B209" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C209" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D209" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E209" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F209" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G209" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H209" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I209" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J209" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K209" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C210" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D210" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E210" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F210" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G210" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H210" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I210" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J210" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K210" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C211" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D211" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E211" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F211" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G211" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H211" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I211" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J211" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K211" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C212" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D212" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E212" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F212" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G212" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H212" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I212" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J212" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K212" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C213" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D213" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E213" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F213" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G213" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H213" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I213" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J213" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K213" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C214" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D214" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E214" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F214" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G214" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H214" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I214" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J214" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K214" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C215" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D215" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E215" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F215" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G215" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H215" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I215" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J215" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K215" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C216" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D216" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E216" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F216" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G216" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H216" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I216" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J216" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K216" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C217" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D217" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E217" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F217" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G217" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H217" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I217" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J217" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K217" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B218" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C218" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D218" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E218" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F218" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G218" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H218" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I218" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J218" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K218" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B219" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C219" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D219" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E219" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F219" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G219" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H219" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I219" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J219" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K219" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B220" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C220" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D220" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E220" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F220" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G220" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H220" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I220" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J220" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K220" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B221" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C221" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D221" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E221" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F221" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G221" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H221" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I221" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J221" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K221" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B222" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C222" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D222" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E222" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F222" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G222" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H222" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I222" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J222" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K222" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B223" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C223" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D223" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E223" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F223" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G223" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H223" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I223" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J223" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K223" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B224" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C224" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D224" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E224" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F224" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G224" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H224" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I224" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J224" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K224" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K224"/>
+  <dimension ref="A1:K225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9248,6 +9248,45 @@
         </is>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B225" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C225" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D225" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E225" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F225" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G225" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H225" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I225" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J225" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K225" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K225"/>
+  <dimension ref="A1:K226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9287,6 +9287,45 @@
         </is>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B226" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C226" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D226" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E226" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F226" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G226" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H226" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I226" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J226" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K226" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K226"/>
+  <dimension ref="A1:K227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9326,6 +9326,45 @@
         </is>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B227" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C227" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D227" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E227" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F227" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G227" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H227" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I227" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J227" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K227" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga Komoditas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harga Komoditas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2033,6 +2033,1527 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K56" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K60" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I61" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I62" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I64" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J64" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I65" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I66" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J66" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I67" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I68" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J68" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G69" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I69" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J69" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I70" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J70" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G71" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H71" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I71" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J71" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I72" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J72" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K72" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I73" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G74" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I74" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J74" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K74" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G75" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I75" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J75" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I76" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J76" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K76" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D77" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G77" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I77" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J77" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D78" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G78" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I78" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J78" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K78" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2034,39 +2034,39 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="n">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
         <v>6494</v>
       </c>
-      <c r="C40" s="6" t="n">
+      <c r="C40" t="n">
         <v>6791</v>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" t="n">
         <v>11809</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" t="n">
         <v>9956</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F40" t="n">
         <v>8351</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="G40" t="n">
         <v>8175</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="H40" t="n">
         <v>6978</v>
       </c>
-      <c r="I40" s="6" t="n">
+      <c r="I40" t="n">
         <v>10037</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="J40" t="n">
         <v>6237</v>
       </c>
-      <c r="K40" s="7" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>fallback</t>
         </is>
@@ -2075,7 +2075,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
@@ -2114,7 +2114,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
@@ -2145,1410 +2145,6 @@
         <v>6237</v>
       </c>
       <c r="K42" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E43" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G43" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H43" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I43" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K43" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C44" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D44" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E44" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G44" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H44" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I44" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J44" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K44" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C45" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D45" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E45" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G45" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H45" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I45" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K45" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C46" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D46" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E46" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F46" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G46" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H46" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I46" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J46" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K46" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C47" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D47" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E47" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G47" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H47" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I47" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J47" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K47" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C48" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D48" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E48" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F48" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G48" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H48" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I48" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J48" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K48" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C49" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D49" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E49" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G49" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H49" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I49" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J49" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K49" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C50" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D50" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E50" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F50" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G50" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H50" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I50" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J50" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K50" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C51" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D51" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E51" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F51" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G51" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H51" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I51" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J51" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C52" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D52" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E52" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F52" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G52" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H52" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I52" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J52" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K52" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C53" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D53" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E53" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G53" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I53" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C54" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D54" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E54" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K54" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C55" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D55" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E55" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I55" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J55" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K55" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C56" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D56" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E56" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I56" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K56" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C57" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D57" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E57" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G57" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I57" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J57" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C58" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D58" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G58" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I58" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J58" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K58" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C59" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D59" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E59" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G59" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H59" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I59" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J59" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C60" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D60" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E60" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F60" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G60" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H60" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I60" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J60" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K60" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C61" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D61" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E61" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F61" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G61" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H61" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I61" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J61" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C62" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D62" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E62" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F62" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G62" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H62" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I62" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J62" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K62" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C63" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D63" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E63" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G63" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H63" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I63" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J63" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K63" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C64" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D64" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E64" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F64" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G64" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H64" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I64" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J64" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K64" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C65" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D65" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E65" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G65" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I65" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J65" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C66" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D66" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E66" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G66" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H66" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I66" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J66" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K66" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C67" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D67" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E67" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F67" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G67" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H67" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I67" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J67" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K67" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C68" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D68" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E68" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F68" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G68" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H68" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I68" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J68" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K68" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C69" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D69" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E69" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F69" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G69" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H69" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I69" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J69" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K69" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C70" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D70" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E70" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F70" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G70" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H70" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I70" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J70" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K70" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C71" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D71" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E71" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F71" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G71" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H71" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I71" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J71" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K71" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C72" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D72" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E72" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F72" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G72" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H72" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I72" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J72" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K72" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C73" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D73" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E73" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F73" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G73" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H73" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I73" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J73" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K73" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C74" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D74" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E74" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F74" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G74" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H74" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I74" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J74" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K74" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C75" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D75" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E75" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F75" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G75" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H75" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I75" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J75" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K75" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C76" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D76" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E76" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F76" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G76" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H76" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I76" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J76" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K76" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C77" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D77" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E77" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F77" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G77" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H77" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I77" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J77" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K77" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C78" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D78" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E78" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F78" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G78" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H78" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I78" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J78" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K78" s="7" t="inlineStr">
         <is>
           <t>fallback</t>
         </is>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harga Komoditas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga Komoditas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2072,84 +2072,6 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D41" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E41" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H41" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I41" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J41" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K41" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="n">
-        <v>6494</v>
-      </c>
-      <c r="C42" s="6" t="n">
-        <v>6791</v>
-      </c>
-      <c r="D42" s="6" t="n">
-        <v>11809</v>
-      </c>
-      <c r="E42" s="6" t="n">
-        <v>9956</v>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G42" s="6" t="n">
-        <v>8175</v>
-      </c>
-      <c r="H42" s="6" t="n">
-        <v>6978</v>
-      </c>
-      <c r="I42" s="6" t="n">
-        <v>10037</v>
-      </c>
-      <c r="J42" s="6" t="n">
-        <v>6237</v>
-      </c>
-      <c r="K42" s="7" t="inlineStr">
-        <is>
-          <t>fallback</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga Komoditas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harga Komoditas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2072,84 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C41" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D41" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F41" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G41" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H41" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I41" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J41" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2112,39 +2112,78 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" t="n">
         <v>6494</v>
       </c>
-      <c r="C42" s="6" t="n">
+      <c r="C42" t="n">
         <v>6791</v>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" t="n">
         <v>11809</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" t="n">
         <v>9956</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F42" t="n">
         <v>8351</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="G42" t="n">
         <v>8175</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="H42" t="n">
         <v>6978</v>
       </c>
-      <c r="I42" s="6" t="n">
+      <c r="I42" t="n">
         <v>10037</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="J42" t="n">
         <v>6237</v>
       </c>
-      <c r="K42" s="7" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
         <is>
           <t>fallback</t>
         </is>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2151,39 +2151,78 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" t="n">
         <v>6494</v>
       </c>
-      <c r="C43" s="6" t="n">
+      <c r="C43" t="n">
         <v>6791</v>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" t="n">
         <v>11809</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E43" t="n">
         <v>9956</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" t="n">
         <v>8351</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="G43" t="n">
         <v>8175</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="H43" t="n">
         <v>6978</v>
       </c>
-      <c r="I43" s="6" t="n">
+      <c r="I43" t="n">
         <v>10037</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="J43" t="n">
         <v>6237</v>
       </c>
-      <c r="K43" s="7" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
         <is>
           <t>fallback</t>
         </is>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harga Komoditas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga Komoditas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2190,39 +2190,78 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" t="n">
         <v>6494</v>
       </c>
-      <c r="C44" s="6" t="n">
+      <c r="C44" t="n">
         <v>6791</v>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" t="n">
         <v>11809</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E44" t="n">
         <v>9956</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" t="n">
         <v>8351</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="G44" t="n">
         <v>8175</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="H44" t="n">
         <v>6978</v>
       </c>
-      <c r="I44" s="6" t="n">
+      <c r="I44" t="n">
         <v>10037</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="J44" t="n">
         <v>6237</v>
       </c>
-      <c r="K44" s="7" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>fallback</t>
         </is>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga Komoditas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harga Komoditas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2229,39 +2229,156 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" t="n">
         <v>6494</v>
       </c>
-      <c r="C45" s="6" t="n">
+      <c r="C45" t="n">
         <v>6791</v>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" t="n">
         <v>11809</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" t="n">
         <v>9956</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" t="n">
         <v>8351</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="G45" t="n">
         <v>8175</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="H45" t="n">
         <v>6978</v>
       </c>
-      <c r="I45" s="6" t="n">
+      <c r="I45" t="n">
         <v>10037</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="J45" t="n">
         <v>6237</v>
       </c>
-      <c r="K45" s="7" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C46" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D46" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E46" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F46" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G46" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H46" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I46" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J46" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C47" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D47" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E47" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F47" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G47" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H47" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I47" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J47" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>fallback</t>
         </is>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2346,39 +2346,117 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" t="n">
         <v>6494</v>
       </c>
-      <c r="C48" s="6" t="n">
+      <c r="C48" t="n">
         <v>6791</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D48" t="n">
         <v>11809</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" t="n">
         <v>9956</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F48" t="n">
         <v>8351</v>
       </c>
-      <c r="G48" s="6" t="n">
+      <c r="G48" t="n">
         <v>8175</v>
       </c>
-      <c r="H48" s="6" t="n">
+      <c r="H48" t="n">
         <v>6978</v>
       </c>
-      <c r="I48" s="6" t="n">
+      <c r="I48" t="n">
         <v>10037</v>
       </c>
-      <c r="J48" s="6" t="n">
+      <c r="J48" t="n">
         <v>6237</v>
       </c>
-      <c r="K48" s="7" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D49" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E49" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G49" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H49" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I49" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J49" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
         <is>
           <t>fallback</t>
         </is>

--- a/data/harga_pertanian_ternak.xlsx
+++ b/data/harga_pertanian_ternak.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2424,39 +2424,351 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" t="n">
         <v>6494</v>
       </c>
-      <c r="C50" s="6" t="n">
+      <c r="C50" t="n">
         <v>6791</v>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="D50" t="n">
         <v>11809</v>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" t="n">
         <v>9956</v>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F50" t="n">
         <v>8351</v>
       </c>
-      <c r="G50" s="6" t="n">
+      <c r="G50" t="n">
         <v>8175</v>
       </c>
-      <c r="H50" s="6" t="n">
+      <c r="H50" t="n">
         <v>6978</v>
       </c>
-      <c r="I50" s="6" t="n">
+      <c r="I50" t="n">
         <v>10037</v>
       </c>
-      <c r="J50" s="6" t="n">
+      <c r="J50" t="n">
         <v>6237</v>
       </c>
-      <c r="K50" s="7" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C51" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D51" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E51" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F51" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G51" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H51" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I51" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J51" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C52" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D52" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E52" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F52" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G52" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H52" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I52" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J52" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C53" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D53" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E53" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F53" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H53" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I53" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J53" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C54" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D54" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E54" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F54" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G54" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H54" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I54" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J54" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C55" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D55" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E55" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F55" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G55" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H55" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I55" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J55" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C56" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D56" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E56" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F56" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G56" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H56" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I56" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J56" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C57" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D57" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E57" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F57" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G57" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H57" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I57" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J57" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>6791</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>11809</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>9956</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>8351</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>10037</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>6237</v>
+      </c>
+      <c r="K58" s="7" t="inlineStr">
         <is>
           <t>fallback</t>
         </is>
